--- a/YSIG/Stock Pitch/RBLX/CF-Export-26-10-2025.xlsx
+++ b/YSIG/Stock Pitch/RBLX/CF-Export-26-10-2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mateo/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mateo/Documents/Notes/YSIG/Stock Pitch/RBLX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4F71D8-6413-2E42-A65F-866B8DAB7144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A38425-67A0-684C-AC5B-87FC9B85A055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,15 +499,6 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -557,6 +548,15 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -871,4247 +871,4190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="5">
         <v>45956.170522523098</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="O11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="P11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="Q11" s="3" t="s">
+      <c r="Q11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="R11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="T11" s="23" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="21">
         <v>45838</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="21">
         <v>45747</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="21">
         <v>45657</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="21">
         <v>45565</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="21">
         <v>45473</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="21">
         <v>45382</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="21">
         <v>45291</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="21">
         <v>45199</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="21">
         <v>45107</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="21">
         <v>45016</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="21">
         <v>44926</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="21">
         <v>44834</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="21">
         <v>44742</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="21">
         <v>44651</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="21">
         <v>44561</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="21">
         <v>44469</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="21">
         <v>44377</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="21">
         <v>44286</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12" s="21">
         <v>44196</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="21">
         <v>45837</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="21">
         <v>45746</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="21">
         <v>45656</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="21">
         <v>45564</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="21">
         <v>45472</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="21">
         <v>45381</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="21">
         <v>45290</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="21">
         <v>45198</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="21">
         <v>45106</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="21">
         <v>45015</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="21">
         <v>44925</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="21">
         <v>44833</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="21">
         <v>44741</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="21">
         <v>44650</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="21">
         <v>44560</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="21">
         <v>44468</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="21">
         <v>44376</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="21">
         <v>44285</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T13" s="21">
         <v>44195</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="N14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="O14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="P14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="Q14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="R14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="S14" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="T14" s="1" t="s">
+      <c r="T14" s="22" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="N15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="O15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="P15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="Q15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="R15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="S15" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="T15" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="L18" s="12" t="s">
+      <c r="L18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N18" s="12" t="s">
+      <c r="N18" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="O18" s="12" t="s">
+      <c r="O18" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="P18" s="12" t="s">
+      <c r="P18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="Q18" s="12" t="s">
+      <c r="Q18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="R18" s="12" t="s">
+      <c r="R18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="S18" s="12" t="s">
+      <c r="S18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="T18" s="12" t="s">
+      <c r="T18" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
     </row>
     <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="13">
         <v>1080677</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="13">
         <v>1035207</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="13">
         <v>988183</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="13">
         <v>918953</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="13">
         <v>893543</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="13">
         <v>801300</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="13">
         <v>749939</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="13">
         <v>713225</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="13">
         <v>680766</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="13">
         <v>655344</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="13">
         <v>579004</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="13">
         <v>517707</v>
       </c>
-      <c r="N20" s="16">
+      <c r="N20" s="13">
         <v>591207</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="13">
         <v>537134</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="13">
         <v>568769</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="13">
         <v>509336</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="13">
         <v>454100</v>
       </c>
-      <c r="S20" s="16">
+      <c r="S20" s="13">
         <v>386976</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="13">
         <v>310009</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="13">
         <v>844564</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="13">
         <v>810482</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="13">
         <v>769442</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="13">
         <v>713955</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="13">
         <v>694986</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="13">
         <v>622434</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="13">
         <v>578275</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="13">
         <v>549644</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="13">
         <v>518737</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="13">
         <v>503503</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="13">
         <v>436572</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="13">
         <v>391270</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="13">
         <v>448050</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O21" s="13">
         <v>401502</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P21" s="13">
         <v>416781</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="13">
         <v>379321</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="13">
         <v>337170</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S21" s="13">
         <v>289039</v>
       </c>
-      <c r="T21" s="16">
+      <c r="T21" s="13">
         <v>231391</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="14">
         <v>-322460</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="14">
         <v>-254709</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="14">
         <v>-243939</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="14">
         <v>-278820</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="14">
         <v>-238138</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="14">
         <v>-301146</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="14">
         <v>-349965</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="14">
         <v>-300038</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="14">
         <v>-313989</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="14">
         <v>-282847</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="14">
         <v>-301899</v>
       </c>
-      <c r="M22" s="17">
+      <c r="M22" s="14">
         <v>-300007</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="14">
         <v>-170267</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="14">
         <v>-151611</v>
       </c>
-      <c r="P22" s="17">
+      <c r="P22" s="14">
         <v>-139650</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="14">
         <v>-77446</v>
       </c>
-      <c r="R22" s="17">
+      <c r="R22" s="14">
         <v>-142946</v>
       </c>
-      <c r="S22" s="17">
+      <c r="S22" s="14">
         <v>-135056</v>
       </c>
-      <c r="T22" s="17">
+      <c r="T22" s="14">
         <v>-68607</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="14">
         <v>-268676</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="14">
         <v>-200909</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="14">
         <v>-192628</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="14">
         <v>-210207</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="14">
         <v>-185338</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="14">
         <v>-247346</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="14">
         <v>-295365</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="14">
         <v>-246438</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="14">
         <v>-261389</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="14">
         <v>-235435</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="14">
         <v>-259299</v>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="14">
         <v>-265955</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="14">
         <v>-141267</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="14">
         <v>-127111</v>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="14">
         <v>-117350</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="14">
         <v>-55717</v>
       </c>
-      <c r="R23" s="17">
+      <c r="R23" s="14">
         <v>-123056</v>
       </c>
-      <c r="S23" s="17">
+      <c r="S23" s="14">
         <v>-116336</v>
       </c>
-      <c r="T23" s="17">
+      <c r="T23" s="14">
         <v>-55031</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="14">
         <v>-279800</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="14">
         <v>-216340</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="14">
         <v>-221052</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="14">
         <v>-240447</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="14">
         <v>-207195</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="14">
         <v>-271920</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="14">
         <v>-325340</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="14">
         <v>-278808</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="14">
         <v>-284841</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="14">
         <v>-269948</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="14">
         <v>-291485</v>
       </c>
-      <c r="M24" s="17">
+      <c r="M24" s="14">
         <v>-301902</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="14">
         <v>-178734</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="14">
         <v>-162020</v>
       </c>
-      <c r="P24" s="17">
+      <c r="P24" s="14">
         <v>-147257</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="14">
         <v>-77190</v>
       </c>
-      <c r="R24" s="17">
+      <c r="R24" s="14">
         <v>-142930</v>
       </c>
-      <c r="S24" s="17">
+      <c r="S24" s="14">
         <v>-136103</v>
       </c>
-      <c r="T24" s="17">
+      <c r="T24" s="14">
         <v>-60537</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
     </row>
     <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="13">
         <v>994570</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="13">
         <v>1158680</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="13">
         <v>711683</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="13">
         <v>602631</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="13">
         <v>966406</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="13">
         <v>866414</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="13">
         <v>678466</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="13">
         <v>580049</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="13">
         <v>520264</v>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="13">
         <v>828129</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="13">
         <v>2977474</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="13">
         <v>3021507</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="13">
         <v>3075475</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="13">
         <v>3132964</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="13">
         <v>3004300</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="13">
         <v>1925559</v>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="13">
         <v>1780262</v>
       </c>
-      <c r="S26" s="16">
+      <c r="S26" s="13">
         <v>1600530</v>
       </c>
-      <c r="T26" s="16">
+      <c r="T26" s="13">
         <v>893943</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="13">
         <v>2627196</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="13">
         <v>2744529</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="13">
         <v>2409545</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="13">
         <v>2322954</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="13">
         <v>2412095</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="13">
         <v>2410233</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="13">
         <v>2193274</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="13">
         <v>2156342</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="13">
         <v>2119866</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="13">
         <v>2240991</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="13">
         <v>2977474</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="13">
         <v>3021507</v>
       </c>
-      <c r="N27" s="16">
+      <c r="N27" s="13">
         <v>3075475</v>
       </c>
-      <c r="O27" s="16">
+      <c r="O27" s="13">
         <v>3132964</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="13">
         <v>3004300</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="13">
         <v>1925559</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="13">
         <v>1780262</v>
       </c>
-      <c r="S27" s="16">
+      <c r="S27" s="13">
         <v>1600530</v>
       </c>
-      <c r="T27" s="16">
+      <c r="T27" s="13">
         <v>893943</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="13">
         <v>7845571</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="13">
         <v>7452249</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="13">
         <v>7175003</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="13">
         <v>6687962</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="13">
         <v>6470516</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="13">
         <v>6314671</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="13">
         <v>6168078</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="13">
         <v>5754130</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="13">
         <v>5599277</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="13">
         <v>5471460</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="13">
         <v>5375487</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="13">
         <v>5038324</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N28" s="13">
         <v>4919420</v>
       </c>
-      <c r="O28" s="16">
+      <c r="O28" s="13">
         <v>4715831</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="13">
         <v>4560596</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="13">
         <v>3272280</v>
       </c>
-      <c r="R28" s="16">
+      <c r="R28" s="13">
         <v>3073791</v>
       </c>
-      <c r="S28" s="16">
+      <c r="S28" s="13">
         <v>2816079</v>
       </c>
-      <c r="T28" s="16">
+      <c r="T28" s="13">
         <v>1847800</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="13">
         <v>1007077</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="13">
         <v>1006722</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="13">
         <v>1006371</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="13">
         <v>1006023</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="13">
         <v>1005679</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="13">
         <v>1005338</v>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="13">
         <v>1005000</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="13">
         <v>1004666</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="13">
         <v>1004335</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="13">
         <v>989308</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="13">
         <v>988984</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="13">
         <v>988663</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="13">
         <v>988345</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O29" s="13">
         <v>988034</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="13">
         <v>987723</v>
       </c>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
     </row>
     <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="13">
         <v>353221</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="13">
         <v>310687</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="13">
         <v>221446</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="13">
         <v>189905</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="13">
         <v>121506</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="13">
         <v>71601</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="13">
         <v>76290</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="13">
         <v>125786</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="13">
         <v>168497</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="13">
         <v>247842</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="13">
         <v>306026</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="13">
         <v>423717</v>
       </c>
-      <c r="N30" s="16">
+      <c r="N30" s="13">
         <v>547088</v>
       </c>
-      <c r="O30" s="16">
+      <c r="O30" s="13">
         <v>561087</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="13">
         <v>584817</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="13">
         <v>593717</v>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="13">
         <v>526690</v>
       </c>
-      <c r="S30" s="16">
+      <c r="S30" s="13">
         <v>573473</v>
       </c>
-      <c r="T30" s="17">
+      <c r="T30" s="14">
         <v>-252388</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="13">
         <v>199262</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="13">
         <v>443914</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="13">
         <v>184491</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="13">
         <v>247430</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="13">
         <v>151449</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="13">
         <v>238946</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="13">
         <v>143305</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="13">
         <v>112704</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="13">
         <v>28390</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="13">
         <v>173781</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="13">
         <v>119219</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="13">
         <v>67144</v>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="13">
         <v>26497</v>
       </c>
-      <c r="O32" s="16">
+      <c r="O32" s="13">
         <v>156436</v>
       </c>
-      <c r="P32" s="16">
+      <c r="P32" s="13">
         <v>122223</v>
       </c>
-      <c r="Q32" s="16">
+      <c r="Q32" s="13">
         <v>181166</v>
       </c>
-      <c r="R32" s="16">
+      <c r="R32" s="13">
         <v>191251</v>
       </c>
-      <c r="S32" s="16">
+      <c r="S32" s="13">
         <v>164469</v>
       </c>
-      <c r="T32" s="16">
+      <c r="T32" s="13">
         <v>179004</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="13">
         <v>58685</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="13">
         <v>53519</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="13">
         <v>52033</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="13">
         <v>70520</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="13">
         <v>53152</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="13">
         <v>53804</v>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="13">
         <v>55753</v>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="13">
         <v>55178</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="13">
         <v>50532</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="13">
         <v>55648</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="13">
         <v>42538</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="13">
         <v>34052</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="13">
         <v>28996</v>
       </c>
-      <c r="O33" s="16">
+      <c r="O33" s="13">
         <v>24497</v>
       </c>
-      <c r="P33" s="16">
+      <c r="P33" s="13">
         <v>22183</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="Q33" s="13">
         <v>19029</v>
       </c>
-      <c r="R33" s="16">
+      <c r="R33" s="13">
         <v>17790</v>
       </c>
-      <c r="S33" s="16">
+      <c r="S33" s="13">
         <v>16620</v>
       </c>
-      <c r="T33" s="16">
+      <c r="T33" s="13">
         <v>13576</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="13">
         <v>22610</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="13">
         <v>17365</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="13">
         <v>63860</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="13">
         <v>29405</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="13">
         <v>39871</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="13">
         <v>47880</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="13">
         <v>65197</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="13">
         <v>53196</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="13">
         <v>123915</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="13">
         <v>91859</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="13">
         <v>157205</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="13">
         <v>134856</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N34" s="13">
         <v>83812</v>
       </c>
-      <c r="O34" s="16">
+      <c r="O34" s="13">
         <v>51790</v>
       </c>
-      <c r="P34" s="16">
+      <c r="P34" s="13">
         <v>44942</v>
       </c>
-      <c r="Q34" s="16">
+      <c r="Q34" s="13">
         <v>10563</v>
       </c>
-      <c r="R34" s="16">
+      <c r="R34" s="13">
         <v>23235</v>
       </c>
-      <c r="S34" s="16">
+      <c r="S34" s="13">
         <v>22389</v>
       </c>
-      <c r="T34" s="16">
+      <c r="T34" s="13">
         <v>60407</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="14">
         <v>-164110</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="13">
         <v>446997</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="13">
         <v>109052</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="14">
         <v>-363775</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="13">
         <v>99992</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="13">
         <v>187948</v>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="13">
         <v>98417</v>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="13">
         <v>59785</v>
       </c>
-      <c r="J35" s="17">
+      <c r="J35" s="14">
         <v>-307865</v>
       </c>
-      <c r="K35" s="17">
+      <c r="K35" s="14">
         <v>-2149345</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="14">
         <v>-44033</v>
       </c>
-      <c r="M35" s="17">
+      <c r="M35" s="14">
         <v>-53968</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="14">
         <v>-57489</v>
       </c>
-      <c r="O35" s="16">
+      <c r="O35" s="13">
         <v>128664</v>
       </c>
-      <c r="P35" s="16">
+      <c r="P35" s="13">
         <v>1078741</v>
       </c>
-      <c r="Q35" s="16">
+      <c r="Q35" s="13">
         <v>145297</v>
       </c>
-      <c r="R35" s="16">
+      <c r="R35" s="13">
         <v>179732</v>
       </c>
-      <c r="S35" s="16">
+      <c r="S35" s="13">
         <v>706587</v>
       </c>
-      <c r="T35" s="16">
+      <c r="T35" s="13">
         <v>92297</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="13">
         <v>176652</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="13">
         <v>426549</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="13">
         <v>120631</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="13">
         <v>218025</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="13">
         <v>111578</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="13">
         <v>191066</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="13">
         <v>78108</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="13">
         <v>59508</v>
       </c>
-      <c r="J36" s="17">
+      <c r="J36" s="14">
         <v>-95525</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="13">
         <v>81922</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="14">
         <v>-37986</v>
       </c>
-      <c r="M36" s="17">
+      <c r="M36" s="14">
         <v>-67712</v>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="14">
         <v>-57315</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O36" s="13">
         <v>104646</v>
       </c>
-      <c r="P36" s="16">
+      <c r="P36" s="13">
         <v>77281</v>
       </c>
-      <c r="Q36" s="16">
+      <c r="Q36" s="13">
         <v>170603</v>
       </c>
-      <c r="R36" s="16">
+      <c r="R36" s="13">
         <v>168016</v>
       </c>
-      <c r="S36" s="16">
+      <c r="S36" s="13">
         <v>142080</v>
       </c>
-      <c r="T36" s="16">
+      <c r="T36" s="13">
         <v>118597</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
     </row>
     <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="16">
         <v>-0.41</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="16">
         <v>-0.32</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="16">
         <v>-0.33</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="16">
         <v>-0.37</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="16">
         <v>-0.32</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="16">
         <v>-0.43</v>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="16">
         <v>-0.52</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="16">
         <v>-0.45</v>
       </c>
-      <c r="J39" s="19">
+      <c r="J39" s="16">
         <v>-0.46</v>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="16">
         <v>-0.44</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="16">
         <v>-0.48</v>
       </c>
-      <c r="M39" s="19">
+      <c r="M39" s="16">
         <v>-0.5</v>
       </c>
-      <c r="N39" s="19">
+      <c r="N39" s="16">
         <v>-0.3</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="16">
         <v>-0.27</v>
       </c>
-      <c r="P39" s="19">
+      <c r="P39" s="16">
         <v>-0.24</v>
       </c>
-      <c r="Q39" s="19">
+      <c r="Q39" s="16">
         <v>-0.13</v>
       </c>
-      <c r="R39" s="19">
+      <c r="R39" s="16">
         <v>-0.24</v>
       </c>
-      <c r="S39" s="19">
+      <c r="S39" s="16">
         <v>-0.24</v>
       </c>
-      <c r="T39" s="19">
+      <c r="T39" s="16">
         <v>-0.11</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="13">
         <v>684837</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="13">
         <v>671657</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="13">
         <v>660997</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="13">
         <v>650961</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="13">
         <v>642814</v>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="13">
         <v>635020</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="13">
         <v>626966</v>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="13">
         <v>619350</v>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="13">
         <v>612689</v>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="13">
         <v>606637</v>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="13">
         <v>601880</v>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="13">
         <v>597779</v>
       </c>
-      <c r="N40" s="16">
+      <c r="N40" s="13">
         <v>593928</v>
       </c>
-      <c r="O40" s="16">
+      <c r="O40" s="13">
         <v>588521</v>
       </c>
-      <c r="P40" s="16">
+      <c r="P40" s="13">
         <v>585878</v>
       </c>
-      <c r="Q40" s="16">
+      <c r="Q40" s="13">
         <v>578471</v>
       </c>
-      <c r="R40" s="16">
+      <c r="R40" s="13">
         <v>574595</v>
       </c>
-      <c r="S40" s="16">
+      <c r="S40" s="13">
         <v>569831.46</v>
       </c>
-      <c r="T40" s="16">
+      <c r="T40" s="13">
         <v>550450.77</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="14"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
     </row>
     <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="13">
         <v>18360</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="13">
         <v>57961</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="14">
         <v>-245387</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="13">
         <v>223366</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="13">
         <v>66525</v>
       </c>
-      <c r="G42" s="20">
+      <c r="G42" s="17">
         <v>-6903</v>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="13">
         <v>259636</v>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="13">
         <v>81064</v>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="13">
         <v>37884</v>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="13">
         <v>53103</v>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="13">
         <v>183015</v>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="13">
         <v>50876</v>
       </c>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+      <c r="P42" s="13"/>
+      <c r="Q42" s="13"/>
+      <c r="R42" s="13"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="13"/>
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="13">
         <v>176652</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="13">
         <v>426549</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="13">
         <v>120631</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="13">
         <v>218025</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="13">
         <v>111578</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="13">
         <v>191066</v>
       </c>
-      <c r="H43" s="16"/>
-      <c r="I43" s="17">
+      <c r="H43" s="13"/>
+      <c r="I43" s="14">
         <v>-32302</v>
       </c>
-      <c r="J43" s="17">
+      <c r="J43" s="14">
         <v>-95525</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="13">
         <v>81922</v>
       </c>
-      <c r="L43" s="17">
+      <c r="L43" s="14">
         <v>-37986</v>
       </c>
-      <c r="M43" s="17">
+      <c r="M43" s="14">
         <v>-67712</v>
       </c>
-      <c r="N43" s="17">
+      <c r="N43" s="14">
         <v>-57315</v>
       </c>
-      <c r="O43" s="16">
+      <c r="O43" s="13">
         <v>104646</v>
       </c>
-      <c r="P43" s="16">
+      <c r="P43" s="13">
         <v>77281</v>
       </c>
-      <c r="Q43" s="16">
+      <c r="Q43" s="13">
         <v>170603</v>
       </c>
-      <c r="R43" s="16">
+      <c r="R43" s="13">
         <v>168016</v>
       </c>
-      <c r="S43" s="16">
+      <c r="S43" s="13">
         <v>142080</v>
       </c>
-      <c r="T43" s="16">
+      <c r="T43" s="13">
         <v>118597</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="14"/>
-      <c r="S44" s="14"/>
-      <c r="T44" s="14"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="11"/>
     </row>
     <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="15">
         <v>78.150000000000006</v>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="15">
         <v>78.290000000000006</v>
       </c>
-      <c r="D45" s="18">
+      <c r="D45" s="15">
         <v>77.86</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="15">
         <v>77.69</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="15">
         <v>77.78</v>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="15">
         <v>77.680000000000007</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="15">
         <v>77.11</v>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="15">
         <v>77.06</v>
       </c>
-      <c r="J45" s="18">
+      <c r="J45" s="15">
         <v>76.2</v>
       </c>
-      <c r="K45" s="18">
+      <c r="K45" s="15">
         <v>76.83</v>
       </c>
-      <c r="L45" s="18">
+      <c r="L45" s="15">
         <v>75.400000000000006</v>
       </c>
-      <c r="M45" s="18">
+      <c r="M45" s="15">
         <v>75.58</v>
       </c>
-      <c r="N45" s="18">
+      <c r="N45" s="15">
         <v>75.790000000000006</v>
       </c>
-      <c r="O45" s="18">
+      <c r="O45" s="15">
         <v>74.75</v>
       </c>
-      <c r="P45" s="18">
+      <c r="P45" s="15">
         <v>73.28</v>
       </c>
-      <c r="Q45" s="18">
+      <c r="Q45" s="15">
         <v>74.47</v>
       </c>
-      <c r="R45" s="18">
+      <c r="R45" s="15">
         <v>74.25</v>
       </c>
-      <c r="S45" s="18">
+      <c r="S45" s="15">
         <v>74.69</v>
       </c>
-      <c r="T45" s="18">
+      <c r="T45" s="15">
         <v>74.64</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="18">
         <v>-24.86</v>
       </c>
-      <c r="C46" s="21">
+      <c r="C46" s="18">
         <v>-19.41</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D46" s="18">
         <v>-19.489999999999998</v>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="18">
         <v>-22.87</v>
       </c>
-      <c r="F46" s="21">
+      <c r="F46" s="18">
         <v>-20.74</v>
       </c>
-      <c r="G46" s="21">
+      <c r="G46" s="18">
         <v>-30.87</v>
       </c>
-      <c r="H46" s="21">
+      <c r="H46" s="18">
         <v>-39.39</v>
       </c>
-      <c r="I46" s="21">
+      <c r="I46" s="18">
         <v>-34.549999999999997</v>
       </c>
-      <c r="J46" s="21">
+      <c r="J46" s="18">
         <v>-38.4</v>
       </c>
-      <c r="K46" s="21">
+      <c r="K46" s="18">
         <v>-35.93</v>
       </c>
-      <c r="L46" s="21">
+      <c r="L46" s="18">
         <v>-44.78</v>
       </c>
-      <c r="M46" s="21">
+      <c r="M46" s="18">
         <v>-51.37</v>
       </c>
-      <c r="N46" s="21">
+      <c r="N46" s="18">
         <v>-23.89</v>
       </c>
-      <c r="O46" s="21">
+      <c r="O46" s="18">
         <v>-23.66</v>
       </c>
-      <c r="P46" s="21">
+      <c r="P46" s="18">
         <v>-20.63</v>
       </c>
-      <c r="Q46" s="21">
+      <c r="Q46" s="18">
         <v>-10.94</v>
       </c>
-      <c r="R46" s="21">
+      <c r="R46" s="18">
         <v>-27.1</v>
       </c>
-      <c r="S46" s="21">
+      <c r="S46" s="18">
         <v>-30.06</v>
       </c>
-      <c r="T46" s="21">
+      <c r="T46" s="18">
         <v>-17.75</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="18">
         <v>-29.84</v>
       </c>
-      <c r="C47" s="21">
+      <c r="C47" s="18">
         <v>-24.6</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="18">
         <v>-24.69</v>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="18">
         <v>-30.34</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="18">
         <v>-26.65</v>
       </c>
-      <c r="G47" s="21">
+      <c r="G47" s="18">
         <v>-37.58</v>
       </c>
-      <c r="H47" s="21">
+      <c r="H47" s="18">
         <v>-46.67</v>
       </c>
-      <c r="I47" s="21">
+      <c r="I47" s="18">
         <v>-42.07</v>
       </c>
-      <c r="J47" s="21">
+      <c r="J47" s="18">
         <v>-46.12</v>
       </c>
-      <c r="K47" s="21">
+      <c r="K47" s="18">
         <v>-43.16</v>
       </c>
-      <c r="L47" s="21">
+      <c r="L47" s="18">
         <v>-52.14</v>
       </c>
-      <c r="M47" s="21">
+      <c r="M47" s="18">
         <v>-57.95</v>
       </c>
-      <c r="N47" s="21">
+      <c r="N47" s="18">
         <v>-28.8</v>
       </c>
-      <c r="O47" s="21">
+      <c r="O47" s="18">
         <v>-28.23</v>
       </c>
-      <c r="P47" s="21">
+      <c r="P47" s="18">
         <v>-24.55</v>
       </c>
-      <c r="Q47" s="21">
+      <c r="Q47" s="18">
         <v>-15.21</v>
       </c>
-      <c r="R47" s="21">
+      <c r="R47" s="18">
         <v>-31.48</v>
       </c>
-      <c r="S47" s="21">
+      <c r="S47" s="18">
         <v>-34.9</v>
       </c>
-      <c r="T47" s="21">
+      <c r="T47" s="18">
         <v>-22.13</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="18">
         <v>-25.8</v>
       </c>
-      <c r="C48" s="21">
+      <c r="C48" s="18">
         <v>-20.81</v>
       </c>
-      <c r="D48" s="21">
+      <c r="D48" s="18">
         <v>-22.1</v>
       </c>
-      <c r="E48" s="21">
+      <c r="E48" s="18">
         <v>-26.13</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="18">
         <v>-23.18</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="18">
         <v>-33.799999999999997</v>
       </c>
-      <c r="H48" s="21">
+      <c r="H48" s="18">
         <v>-43.35</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="18">
         <v>-39</v>
       </c>
-      <c r="J48" s="21">
+      <c r="J48" s="18">
         <v>-42.02</v>
       </c>
-      <c r="K48" s="21">
+      <c r="K48" s="18">
         <v>-41.08</v>
       </c>
-      <c r="L48" s="21">
+      <c r="L48" s="18">
         <v>-49.79</v>
       </c>
-      <c r="M48" s="21">
+      <c r="M48" s="18">
         <v>-58.25</v>
       </c>
-      <c r="N48" s="21">
+      <c r="N48" s="18">
         <v>-30.28</v>
       </c>
-      <c r="O48" s="21">
+      <c r="O48" s="18">
         <v>-30.11</v>
       </c>
-      <c r="P48" s="21">
+      <c r="P48" s="18">
         <v>-25.78</v>
       </c>
-      <c r="Q48" s="21">
+      <c r="Q48" s="18">
         <v>-15.35</v>
       </c>
-      <c r="R48" s="21">
+      <c r="R48" s="18">
         <v>-31.47</v>
       </c>
-      <c r="S48" s="21">
+      <c r="S48" s="18">
         <v>-35.17</v>
       </c>
-      <c r="T48" s="21">
+      <c r="T48" s="18">
         <v>-21.68</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="18">
         <v>-25.89</v>
       </c>
-      <c r="C49" s="21">
+      <c r="C49" s="18">
         <v>-20.9</v>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="18">
         <v>-22.37</v>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="18">
         <v>-26.17</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="18">
         <v>-23.19</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="18">
         <v>-33.93</v>
       </c>
-      <c r="H49" s="21">
+      <c r="H49" s="18">
         <v>-43.38</v>
       </c>
-      <c r="I49" s="21">
+      <c r="I49" s="18">
         <v>-39.090000000000003</v>
       </c>
-      <c r="J49" s="21">
+      <c r="J49" s="18">
         <v>-41.84</v>
       </c>
-      <c r="K49" s="21">
+      <c r="K49" s="18">
         <v>-41.19</v>
       </c>
-      <c r="L49" s="21">
+      <c r="L49" s="18">
         <v>-50.34</v>
       </c>
-      <c r="M49" s="21">
+      <c r="M49" s="18">
         <v>-58.32</v>
       </c>
-      <c r="N49" s="21">
+      <c r="N49" s="18">
         <v>-30.23</v>
       </c>
-      <c r="O49" s="21">
+      <c r="O49" s="18">
         <v>-30.16</v>
       </c>
-      <c r="P49" s="21">
+      <c r="P49" s="18">
         <v>-25.89</v>
       </c>
-      <c r="Q49" s="21">
+      <c r="Q49" s="18">
         <v>-15.16</v>
       </c>
-      <c r="R49" s="21">
+      <c r="R49" s="18">
         <v>-31.48</v>
       </c>
-      <c r="S49" s="21">
+      <c r="S49" s="18">
         <v>-35.17</v>
       </c>
-      <c r="T49" s="21">
+      <c r="T49" s="18">
         <v>-19.53</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="15">
         <v>1.34</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="15">
         <v>2.29</v>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="15">
         <v>1.71</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="15">
         <v>2.12</v>
       </c>
-      <c r="F50" s="18">
+      <c r="F50" s="15">
         <v>1.87</v>
       </c>
-      <c r="G50" s="18">
+      <c r="G50" s="15">
         <v>0.98</v>
       </c>
-      <c r="H50" s="18">
+      <c r="H50" s="15">
         <v>0.44</v>
       </c>
-      <c r="I50" s="18">
+      <c r="I50" s="15">
         <v>0.04</v>
       </c>
-      <c r="J50" s="21">
+      <c r="J50" s="18">
         <v>-0.49</v>
       </c>
-      <c r="K50" s="21">
+      <c r="K50" s="18">
         <v>-0.3</v>
       </c>
-      <c r="L50" s="21">
+      <c r="L50" s="18">
         <v>-0.34</v>
       </c>
-      <c r="M50" s="18">
+      <c r="M50" s="15">
         <v>0.27</v>
       </c>
-      <c r="N50" s="18">
+      <c r="N50" s="15">
         <v>1.53</v>
       </c>
-      <c r="O50" s="18">
+      <c r="O50" s="15">
         <v>1.93</v>
       </c>
-      <c r="P50" s="18">
+      <c r="P50" s="15">
         <v>0.94</v>
       </c>
-      <c r="Q50" s="18">
+      <c r="Q50" s="15">
         <v>1.4</v>
       </c>
-      <c r="R50" s="18">
+      <c r="R50" s="15">
         <v>1.1599999999999999</v>
       </c>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
+      <c r="S50" s="15"/>
+      <c r="T50" s="15"/>
     </row>
     <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="18">
         <v>-401.21</v>
       </c>
-      <c r="C51" s="21">
+      <c r="C51" s="18">
         <v>-460.3</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="18">
         <v>-628.33000000000004</v>
       </c>
-      <c r="E51" s="21">
+      <c r="E51" s="18">
         <v>-658.56</v>
       </c>
-      <c r="F51" s="21">
+      <c r="F51" s="18">
         <v>-742.99</v>
       </c>
-      <c r="G51" s="21">
+      <c r="G51" s="18">
         <v>-722.66</v>
       </c>
-      <c r="H51" s="21">
+      <c r="H51" s="18">
         <v>-602.61</v>
       </c>
-      <c r="I51" s="21">
+      <c r="I51" s="18">
         <v>-406.98</v>
       </c>
-      <c r="J51" s="21">
+      <c r="J51" s="18">
         <v>-318.29000000000002</v>
       </c>
-      <c r="K51" s="21">
+      <c r="K51" s="18">
         <v>-255.27</v>
       </c>
-      <c r="L51" s="21">
+      <c r="L51" s="18">
         <v>-207.53</v>
       </c>
-      <c r="M51" s="21">
+      <c r="M51" s="18">
         <v>-152.88</v>
       </c>
-      <c r="N51" s="21">
+      <c r="N51" s="18">
         <v>-103.18</v>
       </c>
-      <c r="O51" s="21">
+      <c r="O51" s="18">
         <v>-91.25</v>
       </c>
-      <c r="P51" s="21">
+      <c r="P51" s="18">
         <v>-295.79000000000002</v>
       </c>
-      <c r="Q51" s="21">
+      <c r="Q51" s="18">
         <v>-291.02999999999997</v>
       </c>
-      <c r="R51" s="21">
+      <c r="R51" s="18">
         <v>-307.47000000000003</v>
       </c>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
+      <c r="S51" s="15"/>
+      <c r="T51" s="15"/>
     </row>
     <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="18">
         <v>-13.38</v>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="18">
         <v>-12.86</v>
       </c>
-      <c r="D52" s="21">
+      <c r="D52" s="18">
         <v>-14.1</v>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="18">
         <v>-16.8</v>
       </c>
-      <c r="F52" s="21">
+      <c r="F52" s="18">
         <v>-17.95</v>
       </c>
-      <c r="G52" s="21">
+      <c r="G52" s="18">
         <v>-19.7</v>
       </c>
-      <c r="H52" s="21">
+      <c r="H52" s="18">
         <v>-20.079999999999998</v>
       </c>
-      <c r="I52" s="21">
+      <c r="I52" s="18">
         <v>-20.85</v>
       </c>
-      <c r="J52" s="21">
+      <c r="J52" s="18">
         <v>-21.83</v>
       </c>
-      <c r="K52" s="21">
+      <c r="K52" s="18">
         <v>-20.46</v>
       </c>
-      <c r="L52" s="21">
+      <c r="L52" s="18">
         <v>-18.8</v>
       </c>
-      <c r="M52" s="21">
+      <c r="M52" s="18">
         <v>-19.010000000000002</v>
       </c>
-      <c r="N52" s="21">
+      <c r="N52" s="18">
         <v>-14.14</v>
       </c>
-      <c r="O52" s="21">
+      <c r="O52" s="18">
         <v>-14.06</v>
       </c>
-      <c r="P52" s="21">
+      <c r="P52" s="18">
         <v>-15.71</v>
       </c>
-      <c r="Q52" s="21">
+      <c r="Q52" s="18">
         <v>-17.5</v>
       </c>
-      <c r="R52" s="21">
+      <c r="R52" s="18">
         <v>-17.97</v>
       </c>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
+      <c r="S52" s="15"/>
+      <c r="T52" s="15"/>
     </row>
     <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
-      <c r="R53" s="14"/>
-      <c r="S53" s="14"/>
-      <c r="T53" s="14"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
+      <c r="S53" s="11"/>
+      <c r="T53" s="11"/>
     </row>
     <row r="54" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="13">
         <v>1080677</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="13">
         <v>1035207</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="13">
         <v>988183</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="13">
         <v>918953</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="13">
         <v>893543</v>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="13">
         <v>801300</v>
       </c>
-      <c r="H54" s="16">
+      <c r="H54" s="13">
         <v>749939</v>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="13">
         <v>713225</v>
       </c>
-      <c r="J54" s="16">
+      <c r="J54" s="13">
         <v>680766</v>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="13">
         <v>655344</v>
       </c>
-      <c r="L54" s="16">
+      <c r="L54" s="13">
         <v>579004</v>
       </c>
-      <c r="M54" s="16">
+      <c r="M54" s="13">
         <v>517707</v>
       </c>
-      <c r="N54" s="16">
+      <c r="N54" s="13">
         <v>591207</v>
       </c>
-      <c r="O54" s="16">
+      <c r="O54" s="13">
         <v>537134</v>
       </c>
-      <c r="P54" s="16">
+      <c r="P54" s="13">
         <v>568769</v>
       </c>
-      <c r="Q54" s="16">
+      <c r="Q54" s="13">
         <v>509336</v>
       </c>
-      <c r="R54" s="16">
+      <c r="R54" s="13">
         <v>454100</v>
       </c>
-      <c r="S54" s="16">
+      <c r="S54" s="13">
         <v>386976</v>
       </c>
-      <c r="T54" s="16">
+      <c r="T54" s="13">
         <v>310009</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="14">
         <v>-322460</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="14">
         <v>-254709</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="14">
         <v>-243939</v>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="14">
         <v>-278820</v>
       </c>
-      <c r="F55" s="17">
+      <c r="F55" s="14">
         <v>-238138</v>
       </c>
-      <c r="G55" s="17">
+      <c r="G55" s="14">
         <v>-301146</v>
       </c>
-      <c r="H55" s="17">
+      <c r="H55" s="14">
         <v>-349965</v>
       </c>
-      <c r="I55" s="17">
+      <c r="I55" s="14">
         <v>-300038</v>
       </c>
-      <c r="J55" s="17">
+      <c r="J55" s="14">
         <v>-313989</v>
       </c>
-      <c r="K55" s="17">
+      <c r="K55" s="14">
         <v>-282847</v>
       </c>
-      <c r="L55" s="17">
+      <c r="L55" s="14">
         <v>-301899</v>
       </c>
-      <c r="M55" s="17">
+      <c r="M55" s="14">
         <v>-300007</v>
       </c>
-      <c r="N55" s="17">
+      <c r="N55" s="14">
         <v>-170267</v>
       </c>
-      <c r="O55" s="17">
+      <c r="O55" s="14">
         <v>-151611</v>
       </c>
-      <c r="P55" s="17">
+      <c r="P55" s="14">
         <v>-139650</v>
       </c>
-      <c r="Q55" s="17">
+      <c r="Q55" s="14">
         <v>-77446</v>
       </c>
-      <c r="R55" s="17">
+      <c r="R55" s="14">
         <v>-142946</v>
       </c>
-      <c r="S55" s="17">
+      <c r="S55" s="14">
         <v>-135056</v>
       </c>
-      <c r="T55" s="17">
+      <c r="T55" s="14">
         <v>-68607</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="14">
         <v>-268676</v>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="14">
         <v>-200909</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="14">
         <v>-192628</v>
       </c>
-      <c r="E56" s="17">
+      <c r="E56" s="14">
         <v>-210207</v>
       </c>
-      <c r="F56" s="17">
+      <c r="F56" s="14">
         <v>-185338</v>
       </c>
-      <c r="G56" s="17">
+      <c r="G56" s="14">
         <v>-247346</v>
       </c>
-      <c r="H56" s="17">
+      <c r="H56" s="14">
         <v>-295365</v>
       </c>
-      <c r="I56" s="17">
+      <c r="I56" s="14">
         <v>-246438</v>
       </c>
-      <c r="J56" s="17">
+      <c r="J56" s="14">
         <v>-261389</v>
       </c>
-      <c r="K56" s="17">
+      <c r="K56" s="14">
         <v>-235435</v>
       </c>
-      <c r="L56" s="17">
+      <c r="L56" s="14">
         <v>-259299</v>
       </c>
-      <c r="M56" s="17">
+      <c r="M56" s="14">
         <v>-265955</v>
       </c>
-      <c r="N56" s="17">
+      <c r="N56" s="14">
         <v>-141267</v>
       </c>
-      <c r="O56" s="17">
+      <c r="O56" s="14">
         <v>-127111</v>
       </c>
-      <c r="P56" s="17">
+      <c r="P56" s="14">
         <v>-117350</v>
       </c>
-      <c r="Q56" s="17">
+      <c r="Q56" s="14">
         <v>-55717</v>
       </c>
-      <c r="R56" s="17">
+      <c r="R56" s="14">
         <v>-123056</v>
       </c>
-      <c r="S56" s="17">
+      <c r="S56" s="14">
         <v>-116336</v>
       </c>
-      <c r="T56" s="17">
+      <c r="T56" s="14">
         <v>-55031</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="14">
         <v>-279800</v>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="14">
         <v>-216340</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="14">
         <v>-221052</v>
       </c>
-      <c r="E57" s="17">
+      <c r="E57" s="14">
         <v>-240447</v>
       </c>
-      <c r="F57" s="17">
+      <c r="F57" s="14">
         <v>-207195</v>
       </c>
-      <c r="G57" s="17">
+      <c r="G57" s="14">
         <v>-271920</v>
       </c>
-      <c r="H57" s="17">
+      <c r="H57" s="14">
         <v>-325340</v>
       </c>
-      <c r="I57" s="17">
+      <c r="I57" s="14">
         <v>-278808</v>
       </c>
-      <c r="J57" s="17">
+      <c r="J57" s="14">
         <v>-284841</v>
       </c>
-      <c r="K57" s="17">
+      <c r="K57" s="14">
         <v>-269948</v>
       </c>
-      <c r="L57" s="17">
+      <c r="L57" s="14">
         <v>-291485</v>
       </c>
-      <c r="M57" s="17">
+      <c r="M57" s="14">
         <v>-301902</v>
       </c>
-      <c r="N57" s="17">
+      <c r="N57" s="14">
         <v>-178734</v>
       </c>
-      <c r="O57" s="17">
+      <c r="O57" s="14">
         <v>-162020</v>
       </c>
-      <c r="P57" s="17">
+      <c r="P57" s="14">
         <v>-147257</v>
       </c>
-      <c r="Q57" s="17">
+      <c r="Q57" s="14">
         <v>-77190</v>
       </c>
-      <c r="R57" s="17">
+      <c r="R57" s="14">
         <v>-142930</v>
       </c>
-      <c r="S57" s="17">
+      <c r="S57" s="14">
         <v>-136103</v>
       </c>
-      <c r="T57" s="17">
+      <c r="T57" s="14">
         <v>-60537</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="16">
         <v>-0.41</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="16">
         <v>-0.32</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="16">
         <v>-0.33</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="16">
         <v>-0.37</v>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="16">
         <v>-0.32</v>
       </c>
-      <c r="G58" s="19">
+      <c r="G58" s="16">
         <v>-0.43</v>
       </c>
-      <c r="H58" s="19">
+      <c r="H58" s="16">
         <v>-0.52</v>
       </c>
-      <c r="I58" s="19">
+      <c r="I58" s="16">
         <v>-0.45</v>
       </c>
-      <c r="J58" s="19">
+      <c r="J58" s="16">
         <v>-0.46</v>
       </c>
-      <c r="K58" s="19">
+      <c r="K58" s="16">
         <v>-0.44</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="16">
         <v>-0.48</v>
       </c>
-      <c r="M58" s="19">
+      <c r="M58" s="16">
         <v>-0.5</v>
       </c>
-      <c r="N58" s="19">
+      <c r="N58" s="16">
         <v>-0.3</v>
       </c>
-      <c r="O58" s="19">
+      <c r="O58" s="16">
         <v>-0.27</v>
       </c>
-      <c r="P58" s="19">
+      <c r="P58" s="16">
         <v>-0.24</v>
       </c>
-      <c r="Q58" s="19">
+      <c r="Q58" s="16">
         <v>-0.13</v>
       </c>
-      <c r="R58" s="19">
+      <c r="R58" s="16">
         <v>-0.24</v>
       </c>
-      <c r="S58" s="19">
+      <c r="S58" s="16">
         <v>-0.24</v>
       </c>
-      <c r="T58" s="19">
+      <c r="T58" s="16">
         <v>-0.11</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="13">
         <v>693161</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="13">
         <v>677750</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="13">
         <v>666419</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="13">
         <v>656132</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="13">
         <v>646611</v>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="13">
         <v>639734</v>
       </c>
-      <c r="H59" s="16">
+      <c r="H59" s="13">
         <v>631221</v>
       </c>
-      <c r="I59" s="16">
+      <c r="I59" s="13">
         <v>623588</v>
       </c>
-      <c r="J59" s="16">
+      <c r="J59" s="13">
         <v>616301</v>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="13">
         <v>610487</v>
       </c>
-      <c r="L59" s="16">
+      <c r="L59" s="13">
         <v>604674</v>
       </c>
-      <c r="M59" s="16">
+      <c r="M59" s="13">
         <v>600640</v>
       </c>
-      <c r="N59" s="16">
+      <c r="N59" s="13">
         <v>596622</v>
       </c>
-      <c r="O59" s="16">
+      <c r="O59" s="13">
         <v>592195</v>
       </c>
-      <c r="P59" s="16">
+      <c r="P59" s="13">
         <v>585878</v>
       </c>
-      <c r="Q59" s="16">
+      <c r="Q59" s="13">
         <v>578471</v>
       </c>
-      <c r="R59" s="16">
+      <c r="R59" s="13">
         <v>574595</v>
       </c>
-      <c r="S59" s="16">
+      <c r="S59" s="13">
         <v>568894</v>
       </c>
-      <c r="T59" s="16">
+      <c r="T59" s="13">
         <v>550450.77</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-      <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
-      <c r="T60" s="14"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+      <c r="R60" s="11"/>
+      <c r="S60" s="11"/>
+      <c r="T60" s="11"/>
     </row>
     <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="15">
         <v>12.84</v>
       </c>
-      <c r="C61" s="18">
+      <c r="C61" s="15">
         <v>13.51</v>
       </c>
-      <c r="D61" s="18">
+      <c r="D61" s="15">
         <v>14.03</v>
       </c>
-      <c r="E61" s="18">
+      <c r="E61" s="15">
         <v>15.04</v>
       </c>
-      <c r="F61" s="18">
+      <c r="F61" s="15">
         <v>15.54</v>
       </c>
-      <c r="G61" s="18">
+      <c r="G61" s="15">
         <v>15.92</v>
       </c>
-      <c r="H61" s="18">
+      <c r="H61" s="15">
         <v>16.29</v>
       </c>
-      <c r="I61" s="18">
+      <c r="I61" s="15">
         <v>17.46</v>
       </c>
-      <c r="J61" s="18">
+      <c r="J61" s="15">
         <v>17.940000000000001</v>
       </c>
-      <c r="K61" s="18">
+      <c r="K61" s="15">
         <v>18.079999999999998</v>
       </c>
-      <c r="L61" s="18">
+      <c r="L61" s="15">
         <v>18.399999999999999</v>
       </c>
-      <c r="M61" s="18">
+      <c r="M61" s="15">
         <v>19.62</v>
       </c>
-      <c r="N61" s="18">
+      <c r="N61" s="15">
         <v>20.09</v>
       </c>
-      <c r="O61" s="18">
+      <c r="O61" s="15">
         <v>20.95</v>
       </c>
-      <c r="P61" s="18">
+      <c r="P61" s="15">
         <v>21.66</v>
       </c>
-      <c r="Q61" s="18"/>
-      <c r="R61" s="18"/>
-      <c r="S61" s="18"/>
-      <c r="T61" s="18"/>
+      <c r="Q61" s="15"/>
+      <c r="R61" s="15"/>
+      <c r="S61" s="15"/>
+      <c r="T61" s="15"/>
     </row>
     <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="15">
         <v>74.89</v>
       </c>
-      <c r="C62" s="18">
+      <c r="C62" s="15">
         <v>77.239999999999995</v>
       </c>
-      <c r="D62" s="18">
+      <c r="D62" s="15">
         <v>82.83</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="15">
         <v>84.93</v>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="15">
         <v>90.04</v>
       </c>
-      <c r="G62" s="18">
+      <c r="G62" s="15">
         <v>94.13</v>
       </c>
-      <c r="H62" s="18">
+      <c r="H62" s="15">
         <v>93.61</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="15">
         <v>89.34</v>
       </c>
-      <c r="J62" s="18">
+      <c r="J62" s="15">
         <v>85.95</v>
       </c>
-      <c r="K62" s="18">
+      <c r="K62" s="15">
         <v>80.14</v>
       </c>
-      <c r="L62" s="18">
+      <c r="L62" s="15">
         <v>76.430000000000007</v>
       </c>
-      <c r="M62" s="18">
+      <c r="M62" s="15">
         <v>69.959999999999994</v>
       </c>
-      <c r="N62" s="18">
+      <c r="N62" s="15">
         <v>64.180000000000007</v>
       </c>
-      <c r="O62" s="18">
+      <c r="O62" s="15">
         <v>63.52</v>
       </c>
-      <c r="P62" s="18">
+      <c r="P62" s="15">
         <v>62.49</v>
       </c>
-      <c r="Q62" s="18"/>
-      <c r="R62" s="18"/>
-      <c r="S62" s="18"/>
-      <c r="T62" s="18"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="15"/>
+      <c r="S62" s="15"/>
+      <c r="T62" s="15"/>
     </row>
     <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="15">
         <v>298.26</v>
       </c>
-      <c r="C63" s="18">
+      <c r="C63" s="15">
         <v>339.43</v>
       </c>
-      <c r="D63" s="18">
+      <c r="D63" s="15">
         <v>482.32</v>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="15">
         <v>563.73</v>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="15">
         <v>903.57</v>
       </c>
-      <c r="G63" s="18">
+      <c r="G63" s="15">
         <v>1603.74</v>
       </c>
-      <c r="H63" s="18">
+      <c r="H63" s="15">
         <v>1464.46</v>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="15">
         <v>838.24</v>
       </c>
-      <c r="J63" s="18">
+      <c r="J63" s="15">
         <v>611.65</v>
       </c>
-      <c r="K63" s="18">
+      <c r="K63" s="15">
         <v>403.5</v>
       </c>
-      <c r="L63" s="18">
+      <c r="L63" s="15">
         <v>324.22000000000003</v>
       </c>
-      <c r="M63" s="18">
+      <c r="M63" s="15">
         <v>232.85</v>
       </c>
-      <c r="N63" s="18">
+      <c r="N63" s="15">
         <v>179.18</v>
       </c>
-      <c r="O63" s="18">
+      <c r="O63" s="15">
         <v>174.11</v>
       </c>
-      <c r="P63" s="18">
+      <c r="P63" s="15">
         <v>166.59</v>
       </c>
-      <c r="Q63" s="18"/>
-      <c r="R63" s="18"/>
-      <c r="S63" s="18"/>
-      <c r="T63" s="18"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="15"/>
+      <c r="T63" s="15"/>
     </row>
     <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="16">
         <v>-31.18</v>
       </c>
-      <c r="C64" s="19">
+      <c r="C64" s="16">
         <v>-24.61</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="16">
         <v>-23.61</v>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="16">
         <v>-27.11</v>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="16">
         <v>-23.34</v>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="16">
         <v>-29.06</v>
       </c>
-      <c r="H64" s="19">
+      <c r="H64" s="16">
         <v>-33.979999999999997</v>
       </c>
-      <c r="I64" s="19">
+      <c r="I64" s="16">
         <v>-29.22</v>
       </c>
-      <c r="J64" s="19">
+      <c r="J64" s="16">
         <v>-31</v>
       </c>
-      <c r="K64" s="19">
+      <c r="K64" s="16">
         <v>-28.25</v>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="16">
         <v>-30.17</v>
       </c>
-      <c r="M64" s="19">
+      <c r="M64" s="16">
         <v>-29.99</v>
       </c>
-      <c r="N64" s="19">
+      <c r="N64" s="16">
         <v>-17.21</v>
       </c>
-      <c r="O64" s="19">
+      <c r="O64" s="16">
         <v>-15.16</v>
       </c>
-      <c r="P64" s="19">
+      <c r="P64" s="16">
         <v>-19.96</v>
       </c>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
-      <c r="S64" s="16"/>
-      <c r="T64" s="16"/>
+      <c r="Q64" s="13"/>
+      <c r="R64" s="13"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="13"/>
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="14"/>
-      <c r="P65" s="14"/>
-      <c r="Q65" s="14"/>
-      <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
-      <c r="T65" s="14"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
+      <c r="Q65" s="11"/>
+      <c r="R65" s="11"/>
+      <c r="S65" s="11"/>
+      <c r="T65" s="11"/>
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="13">
         <v>72920537.200000003</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="13">
         <v>39506047.5</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="13">
         <v>38559003.340000004</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="13">
         <v>29040402.32</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="13">
         <v>23804468.949999999</v>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="13">
         <v>24410538.010000002</v>
       </c>
-      <c r="H66" s="16">
+      <c r="H66" s="13">
         <v>28517255.550000001</v>
       </c>
-      <c r="I66" s="16">
+      <c r="I66" s="13">
         <v>17861663.079999998</v>
       </c>
-      <c r="J66" s="16">
+      <c r="J66" s="13">
         <v>24836930.300000001</v>
       </c>
-      <c r="K66" s="16">
+      <c r="K66" s="13">
         <v>27459705.260000002</v>
       </c>
-      <c r="L66" s="16">
+      <c r="L66" s="13">
         <v>17099225.949999999</v>
       </c>
-      <c r="M66" s="16">
+      <c r="M66" s="13">
         <v>21526937.600000001</v>
       </c>
-      <c r="N66" s="16">
+      <c r="N66" s="13">
         <v>19604998.920000002</v>
       </c>
-      <c r="O66" s="16">
+      <c r="O66" s="13">
         <v>27383110.760000002</v>
       </c>
-      <c r="P66" s="16">
+      <c r="P66" s="13">
         <v>60439205.630000003</v>
       </c>
-      <c r="Q66" s="16">
+      <c r="Q66" s="13">
         <v>43452750.670000002</v>
       </c>
-      <c r="R66" s="16">
+      <c r="R66" s="13">
         <v>51273435.039999999</v>
       </c>
-      <c r="S66" s="16">
+      <c r="S66" s="13">
         <v>35691537.240000002</v>
       </c>
-      <c r="T66" s="16"/>
+      <c r="T66" s="13"/>
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="13">
         <v>1007077</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="13">
         <v>1006722</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="13">
         <v>1006371</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="13">
         <v>1006023</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="13">
         <v>1005679</v>
       </c>
-      <c r="G67" s="16">
+      <c r="G67" s="13">
         <v>1005338</v>
       </c>
-      <c r="H67" s="16">
+      <c r="H67" s="13">
         <v>1005000</v>
       </c>
-      <c r="I67" s="16">
+      <c r="I67" s="13">
         <v>1004666</v>
       </c>
-      <c r="J67" s="16">
+      <c r="J67" s="13">
         <v>1004335</v>
       </c>
-      <c r="K67" s="16">
+      <c r="K67" s="13">
         <v>989308</v>
       </c>
-      <c r="L67" s="16">
+      <c r="L67" s="13">
         <v>988984</v>
       </c>
-      <c r="M67" s="16">
+      <c r="M67" s="13">
         <v>988663</v>
       </c>
-      <c r="N67" s="16">
+      <c r="N67" s="13">
         <v>988345</v>
       </c>
-      <c r="O67" s="16">
+      <c r="O67" s="13">
         <v>988034</v>
       </c>
-      <c r="P67" s="16">
+      <c r="P67" s="13">
         <v>987723</v>
       </c>
-      <c r="Q67" s="16"/>
-      <c r="R67" s="16"/>
-      <c r="S67" s="16"/>
-      <c r="T67" s="16"/>
+      <c r="Q67" s="13"/>
+      <c r="R67" s="13"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="13"/>
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="16"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="16"/>
-      <c r="O68" s="16"/>
-      <c r="P68" s="16"/>
-      <c r="Q68" s="16"/>
-      <c r="R68" s="16"/>
-      <c r="S68" s="16"/>
-      <c r="T68" s="16">
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="13"/>
+      <c r="R68" s="13"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="13">
         <v>344827</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="14">
         <v>-15565</v>
       </c>
-      <c r="C69" s="17">
+      <c r="C69" s="14">
         <v>-14092</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D69" s="14">
         <v>-12792</v>
       </c>
-      <c r="E69" s="17">
+      <c r="E69" s="14">
         <v>-11447</v>
       </c>
-      <c r="F69" s="17">
+      <c r="F69" s="14">
         <v>-10205</v>
       </c>
-      <c r="G69" s="20">
+      <c r="G69" s="17">
         <v>-8914</v>
       </c>
-      <c r="H69" s="20">
+      <c r="H69" s="17">
         <v>-7664</v>
       </c>
-      <c r="I69" s="20">
+      <c r="I69" s="17">
         <v>-5932</v>
       </c>
-      <c r="J69" s="20">
+      <c r="J69" s="17">
         <v>-4297</v>
       </c>
-      <c r="K69" s="20">
+      <c r="K69" s="17">
         <v>-2660</v>
       </c>
-      <c r="L69" s="20">
+      <c r="L69" s="17">
         <v>-991</v>
       </c>
-      <c r="M69" s="22">
+      <c r="M69" s="19">
         <v>876</v>
       </c>
-      <c r="N69" s="22">
+      <c r="N69" s="19">
         <v>4505</v>
       </c>
-      <c r="O69" s="22">
+      <c r="O69" s="19">
         <v>6374</v>
       </c>
-      <c r="P69" s="22">
+      <c r="P69" s="19">
         <v>8106</v>
       </c>
-      <c r="Q69" s="16">
+      <c r="Q69" s="13">
         <v>12114</v>
       </c>
-      <c r="R69" s="16">
+      <c r="R69" s="13">
         <v>15349</v>
       </c>
-      <c r="S69" s="16">
+      <c r="S69" s="13">
         <v>18121</v>
       </c>
-      <c r="T69" s="16">
+      <c r="T69" s="13">
         <v>20007</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="13">
         <v>2627196</v>
       </c>
-      <c r="C70" s="16">
+      <c r="C70" s="13">
         <v>2744529</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="13">
         <v>2409545</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="13">
         <v>2322954</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="13">
         <v>2412095</v>
       </c>
-      <c r="G70" s="16">
+      <c r="G70" s="13">
         <v>2410233</v>
       </c>
-      <c r="H70" s="16">
+      <c r="H70" s="13">
         <v>2193274</v>
       </c>
-      <c r="I70" s="16">
+      <c r="I70" s="13">
         <v>2156342</v>
       </c>
-      <c r="J70" s="16">
+      <c r="J70" s="13">
         <v>2119866</v>
       </c>
-      <c r="K70" s="16">
+      <c r="K70" s="13">
         <v>2240991</v>
       </c>
-      <c r="L70" s="16">
+      <c r="L70" s="13">
         <v>2977474</v>
       </c>
-      <c r="M70" s="16">
+      <c r="M70" s="13">
         <v>3021507</v>
       </c>
-      <c r="N70" s="16">
+      <c r="N70" s="13">
         <v>3075475</v>
       </c>
-      <c r="O70" s="16">
+      <c r="O70" s="13">
         <v>3132964</v>
       </c>
-      <c r="P70" s="16">
+      <c r="P70" s="13">
         <v>3004300</v>
       </c>
-      <c r="Q70" s="16">
+      <c r="Q70" s="13">
         <v>1925559</v>
       </c>
-      <c r="R70" s="16">
+      <c r="R70" s="13">
         <v>1780262</v>
       </c>
-      <c r="S70" s="16">
+      <c r="S70" s="13">
         <v>1600530</v>
       </c>
-      <c r="T70" s="16">
+      <c r="T70" s="13">
         <v>893943</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="13">
         <v>71284853.200000003</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="13">
         <v>37754148.5</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="13">
         <v>37143037.340000004</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="13">
         <v>27712024.32</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="13">
         <v>22387847.949999999</v>
       </c>
-      <c r="G71" s="16">
+      <c r="G71" s="13">
         <v>22996729.010000002</v>
       </c>
-      <c r="H71" s="16">
+      <c r="H71" s="13">
         <v>27321317.550000001</v>
       </c>
-      <c r="I71" s="16">
+      <c r="I71" s="13">
         <v>16704055.08</v>
       </c>
-      <c r="J71" s="16">
+      <c r="J71" s="13">
         <v>23717102.300000001</v>
       </c>
-      <c r="K71" s="16">
+      <c r="K71" s="13">
         <v>26205362.260000002</v>
       </c>
-      <c r="L71" s="16">
+      <c r="L71" s="13">
         <v>15109744.949999999</v>
       </c>
-      <c r="M71" s="16">
+      <c r="M71" s="13">
         <v>19494969.600000001</v>
       </c>
-      <c r="N71" s="16">
+      <c r="N71" s="13">
         <v>17522373.920000002</v>
       </c>
-      <c r="O71" s="16">
+      <c r="O71" s="13">
         <v>25244554.760000002</v>
       </c>
-      <c r="P71" s="16">
+      <c r="P71" s="13">
         <v>58430734.630000003</v>
       </c>
-      <c r="Q71" s="16">
+      <c r="Q71" s="13">
         <v>41539305.670000002</v>
       </c>
-      <c r="R71" s="16">
+      <c r="R71" s="13">
         <v>49508522.039999999</v>
       </c>
-      <c r="S71" s="16">
+      <c r="S71" s="13">
         <v>34109128.240000002</v>
       </c>
-      <c r="T71" s="16"/>
+      <c r="T71" s="13"/>
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="14"/>
-      <c r="O72" s="14"/>
-      <c r="P72" s="14"/>
-      <c r="Q72" s="14"/>
-      <c r="R72" s="14"/>
-      <c r="S72" s="14"/>
-      <c r="T72" s="14"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="11"/>
+      <c r="P72" s="11"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
+      <c r="T72" s="11"/>
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="20">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C73" s="23">
+      <c r="C73" s="20">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D73" s="20">
         <v>0.54</v>
       </c>
-      <c r="E73" s="23">
+      <c r="E73" s="20">
         <v>0.54</v>
       </c>
-      <c r="F73" s="23">
+      <c r="F73" s="20">
         <v>0.52</v>
       </c>
-      <c r="G73" s="23">
+      <c r="G73" s="20">
         <v>0.5</v>
       </c>
-      <c r="H73" s="23">
+      <c r="H73" s="20">
         <v>0.48</v>
       </c>
-      <c r="I73" s="23">
+      <c r="I73" s="20">
         <v>0.49</v>
       </c>
-      <c r="J73" s="23">
+      <c r="J73" s="20">
         <v>0.46</v>
       </c>
-      <c r="K73" s="23">
+      <c r="K73" s="20">
         <v>0.46</v>
       </c>
-      <c r="L73" s="23">
+      <c r="L73" s="20">
         <v>0.45</v>
       </c>
-      <c r="M73" s="23">
+      <c r="M73" s="20">
         <v>0.53</v>
       </c>
-      <c r="N73" s="23">
+      <c r="N73" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O73" s="23">
+      <c r="O73" s="20">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P73" s="23">
+      <c r="P73" s="20">
         <v>0.6</v>
       </c>
-      <c r="Q73" s="23">
+      <c r="Q73" s="20">
         <v>0.7</v>
       </c>
-      <c r="R73" s="23">
+      <c r="R73" s="20">
         <v>0.65</v>
       </c>
-      <c r="S73" s="16"/>
-      <c r="T73" s="16"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="13"/>
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B74" s="21">
+      <c r="B74" s="18">
         <v>-23.68</v>
       </c>
-      <c r="C74" s="21">
+      <c r="C74" s="18">
         <v>-22.97</v>
       </c>
-      <c r="D74" s="21">
+      <c r="D74" s="18">
         <v>-26</v>
       </c>
-      <c r="E74" s="21">
+      <c r="E74" s="18">
         <v>-31.01</v>
       </c>
-      <c r="F74" s="21">
+      <c r="F74" s="18">
         <v>-34.229999999999997</v>
       </c>
-      <c r="G74" s="21">
+      <c r="G74" s="18">
         <v>-39.39</v>
       </c>
-      <c r="H74" s="21">
+      <c r="H74" s="18">
         <v>-41.39</v>
       </c>
-      <c r="I74" s="21">
+      <c r="I74" s="18">
         <v>-42.68</v>
       </c>
-      <c r="J74" s="21">
+      <c r="J74" s="18">
         <v>-47.07</v>
       </c>
-      <c r="K74" s="21">
+      <c r="K74" s="18">
         <v>-44.3</v>
       </c>
-      <c r="L74" s="21">
+      <c r="L74" s="18">
         <v>-41.82</v>
       </c>
-      <c r="M74" s="21">
+      <c r="M74" s="18">
         <v>-35.619999999999997</v>
       </c>
-      <c r="N74" s="21">
+      <c r="N74" s="18">
         <v>-25.63</v>
       </c>
-      <c r="O74" s="21">
+      <c r="O74" s="18">
         <v>-25.59</v>
       </c>
-      <c r="P74" s="21">
+      <c r="P74" s="18">
         <v>-26.25</v>
       </c>
-      <c r="Q74" s="21">
+      <c r="Q74" s="18">
         <v>-25.56</v>
       </c>
-      <c r="R74" s="21">
+      <c r="R74" s="18">
         <v>-28.24</v>
       </c>
-      <c r="S74" s="21">
+      <c r="S74" s="18">
         <v>-28.33</v>
       </c>
-      <c r="T74" s="21">
+      <c r="T74" s="18">
         <v>-28.61</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B75" s="21">
+      <c r="B75" s="18">
         <v>-13.31</v>
       </c>
-      <c r="C75" s="21">
+      <c r="C75" s="18">
         <v>-12.8</v>
       </c>
-      <c r="D75" s="21">
+      <c r="D75" s="18">
         <v>-14.04</v>
       </c>
-      <c r="E75" s="21">
+      <c r="E75" s="18">
         <v>-16.77</v>
       </c>
-      <c r="F75" s="21">
+      <c r="F75" s="18">
         <v>-17.91</v>
       </c>
-      <c r="G75" s="21">
+      <c r="G75" s="18">
         <v>-19.690000000000001</v>
       </c>
-      <c r="H75" s="21">
+      <c r="H75" s="18">
         <v>-20.07</v>
       </c>
-      <c r="I75" s="21">
+      <c r="I75" s="18">
         <v>-20.79</v>
       </c>
-      <c r="J75" s="21">
+      <c r="J75" s="18">
         <v>-21.77</v>
       </c>
-      <c r="K75" s="21">
+      <c r="K75" s="18">
         <v>-20.38</v>
       </c>
-      <c r="L75" s="21">
+      <c r="L75" s="18">
         <v>-18.73</v>
       </c>
-      <c r="M75" s="21">
+      <c r="M75" s="18">
         <v>-18.989999999999998</v>
       </c>
-      <c r="N75" s="21">
+      <c r="N75" s="18">
         <v>-14.15</v>
       </c>
-      <c r="O75" s="21">
+      <c r="O75" s="18">
         <v>-14.06</v>
       </c>
-      <c r="P75" s="21">
+      <c r="P75" s="18">
         <v>-15.72</v>
       </c>
-      <c r="Q75" s="21">
+      <c r="Q75" s="18">
         <v>-17.829999999999998</v>
       </c>
-      <c r="R75" s="21">
+      <c r="R75" s="18">
         <v>-18.28</v>
       </c>
-      <c r="S75" s="18"/>
-      <c r="T75" s="18"/>
+      <c r="S75" s="15"/>
+      <c r="T75" s="15"/>
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B76" s="20">
         <v>31.89</v>
       </c>
-      <c r="C76" s="23">
+      <c r="C76" s="20">
         <v>38.32</v>
       </c>
-      <c r="D76" s="23">
+      <c r="D76" s="20">
         <v>48.12</v>
       </c>
-      <c r="E76" s="23">
+      <c r="E76" s="20">
         <v>41.71</v>
       </c>
-      <c r="F76" s="23">
+      <c r="F76" s="20">
         <v>43.81</v>
       </c>
-      <c r="G76" s="23">
+      <c r="G76" s="20">
         <v>38.28</v>
       </c>
-      <c r="H76" s="23">
+      <c r="H76" s="20">
         <v>30.89</v>
       </c>
-      <c r="I76" s="23">
+      <c r="I76" s="20">
         <v>19.82</v>
       </c>
-      <c r="J76" s="23">
+      <c r="J76" s="20">
         <v>14.7</v>
       </c>
-      <c r="K76" s="23">
+      <c r="K76" s="20">
         <v>12.54</v>
       </c>
-      <c r="L76" s="23">
+      <c r="L76" s="20">
         <v>11.07</v>
       </c>
-      <c r="M76" s="23">
+      <c r="M76" s="20">
         <v>8.07</v>
       </c>
-      <c r="N76" s="23">
+      <c r="N76" s="20">
         <v>7.31</v>
       </c>
-      <c r="O76" s="23">
+      <c r="O76" s="20">
         <v>6.5</v>
       </c>
-      <c r="P76" s="23">
+      <c r="P76" s="20">
         <v>9.09</v>
       </c>
-      <c r="Q76" s="23">
+      <c r="Q76" s="20">
         <v>7.23</v>
       </c>
-      <c r="R76" s="23">
+      <c r="R76" s="20">
         <v>6.86</v>
       </c>
-      <c r="S76" s="16"/>
-      <c r="T76" s="16"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="13"/>
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B77" s="21">
+      <c r="B77" s="18">
         <v>-424.47</v>
       </c>
-      <c r="C77" s="21">
+      <c r="C77" s="18">
         <v>-490.48</v>
       </c>
-      <c r="D77" s="21">
+      <c r="D77" s="18">
         <v>-675.49</v>
       </c>
-      <c r="E77" s="21">
+      <c r="E77" s="18">
         <v>-699.37</v>
       </c>
-      <c r="F77" s="21">
+      <c r="F77" s="18">
         <v>-784.85</v>
       </c>
-      <c r="G77" s="21">
+      <c r="G77" s="18">
         <v>-753.65</v>
       </c>
-      <c r="H77" s="21">
+      <c r="H77" s="18">
         <v>-620.07000000000005</v>
       </c>
-      <c r="I77" s="21">
+      <c r="I77" s="18">
         <v>-412.05</v>
       </c>
-      <c r="J77" s="21">
+      <c r="J77" s="18">
         <v>-319.95999999999998</v>
       </c>
-      <c r="K77" s="21">
+      <c r="K77" s="18">
         <v>-255.48</v>
       </c>
-      <c r="L77" s="21">
+      <c r="L77" s="18">
         <v>-207.27</v>
       </c>
-      <c r="M77" s="21">
+      <c r="M77" s="18">
         <v>-153.12</v>
       </c>
-      <c r="N77" s="21">
+      <c r="N77" s="18">
         <v>-103.43</v>
       </c>
-      <c r="O77" s="21">
+      <c r="O77" s="18">
         <v>-91.36</v>
       </c>
-      <c r="P77" s="21">
+      <c r="P77" s="18">
         <v>-142.85</v>
       </c>
-      <c r="Q77" s="21">
+      <c r="Q77" s="18">
         <v>-128.86000000000001</v>
       </c>
-      <c r="R77" s="21">
+      <c r="R77" s="18">
         <v>-125.42</v>
       </c>
-      <c r="S77" s="18"/>
-      <c r="T77" s="18"/>
+      <c r="S77" s="15"/>
+      <c r="T77" s="15"/>
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="21">
+      <c r="B78" s="18">
         <v>-401.21</v>
       </c>
-      <c r="C78" s="21">
+      <c r="C78" s="18">
         <v>-460.3</v>
       </c>
-      <c r="D78" s="21">
+      <c r="D78" s="18">
         <v>-628.33000000000004</v>
       </c>
-      <c r="E78" s="21">
+      <c r="E78" s="18">
         <v>-658.56</v>
       </c>
-      <c r="F78" s="21">
+      <c r="F78" s="18">
         <v>-742.99</v>
       </c>
-      <c r="G78" s="21">
+      <c r="G78" s="18">
         <v>-722.66</v>
       </c>
-      <c r="H78" s="21">
+      <c r="H78" s="18">
         <v>-602.61</v>
       </c>
-      <c r="I78" s="21">
+      <c r="I78" s="18">
         <v>-406.98</v>
       </c>
-      <c r="J78" s="21">
+      <c r="J78" s="18">
         <v>-318.29000000000002</v>
       </c>
-      <c r="K78" s="21">
+      <c r="K78" s="18">
         <v>-255.27</v>
       </c>
-      <c r="L78" s="21">
+      <c r="L78" s="18">
         <v>-207.53</v>
       </c>
-      <c r="M78" s="21">
+      <c r="M78" s="18">
         <v>-152.88</v>
       </c>
-      <c r="N78" s="21">
+      <c r="N78" s="18">
         <v>-103.18</v>
       </c>
-      <c r="O78" s="21">
+      <c r="O78" s="18">
         <v>-91.25</v>
       </c>
-      <c r="P78" s="21">
+      <c r="P78" s="18">
         <v>-295.79000000000002</v>
       </c>
-      <c r="Q78" s="21">
+      <c r="Q78" s="18">
         <v>-291.02999999999997</v>
       </c>
-      <c r="R78" s="21">
+      <c r="R78" s="18">
         <v>-307.47000000000003</v>
       </c>
-      <c r="S78" s="18"/>
-      <c r="T78" s="18"/>
+      <c r="S78" s="15"/>
+      <c r="T78" s="15"/>
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B79" s="21">
+      <c r="B79" s="18">
         <v>-401.21</v>
       </c>
-      <c r="C79" s="21">
+      <c r="C79" s="18">
         <v>-460.3</v>
       </c>
-      <c r="D79" s="21">
+      <c r="D79" s="18">
         <v>-628.33000000000004</v>
       </c>
-      <c r="E79" s="21">
+      <c r="E79" s="18">
         <v>-658.56</v>
       </c>
-      <c r="F79" s="21">
+      <c r="F79" s="18">
         <v>-742.99</v>
       </c>
-      <c r="G79" s="21">
+      <c r="G79" s="18">
         <v>-722.66</v>
       </c>
-      <c r="H79" s="21">
+      <c r="H79" s="18">
         <v>-602.61</v>
       </c>
-      <c r="I79" s="21">
+      <c r="I79" s="18">
         <v>-406.98</v>
       </c>
-      <c r="J79" s="21">
+      <c r="J79" s="18">
         <v>-318.29000000000002</v>
       </c>
-      <c r="K79" s="21">
+      <c r="K79" s="18">
         <v>-255.27</v>
       </c>
-      <c r="L79" s="21">
+      <c r="L79" s="18">
         <v>-207.53</v>
       </c>
-      <c r="M79" s="21">
+      <c r="M79" s="18">
         <v>-152.88</v>
       </c>
-      <c r="N79" s="21">
+      <c r="N79" s="18">
         <v>-103.18</v>
       </c>
-      <c r="O79" s="21">
+      <c r="O79" s="18">
         <v>-91.25</v>
       </c>
-      <c r="P79" s="21">
+      <c r="P79" s="18">
         <v>-295.79000000000002</v>
       </c>
-      <c r="Q79" s="21">
+      <c r="Q79" s="18">
         <v>-291.02999999999997</v>
       </c>
-      <c r="R79" s="21">
+      <c r="R79" s="18">
         <v>-307.47000000000003</v>
       </c>
-      <c r="S79" s="18"/>
-      <c r="T79" s="18"/>
+      <c r="S79" s="15"/>
+      <c r="T79" s="15"/>
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="14"/>
-      <c r="O80" s="14"/>
-      <c r="P80" s="14"/>
-      <c r="Q80" s="14"/>
-      <c r="R80" s="14"/>
-      <c r="S80" s="14"/>
-      <c r="T80" s="14"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="11"/>
+      <c r="O80" s="11"/>
+      <c r="P80" s="11"/>
+      <c r="Q80" s="11"/>
+      <c r="R80" s="11"/>
+      <c r="S80" s="11"/>
+      <c r="T80" s="11"/>
     </row>
     <row r="81" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="15" t="s">
+      <c r="A81" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B81" s="20">
         <v>0.97</v>
       </c>
-      <c r="C81" s="23">
+      <c r="C81" s="20">
         <v>1.02</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D81" s="20">
         <v>1.02</v>
       </c>
-      <c r="E81" s="23">
+      <c r="E81" s="20">
         <v>0.98</v>
       </c>
-      <c r="F81" s="23">
+      <c r="F81" s="20">
         <v>1.03</v>
       </c>
-      <c r="G81" s="23">
+      <c r="G81" s="20">
         <v>1.07</v>
       </c>
-      <c r="H81" s="23">
+      <c r="H81" s="20">
         <v>1.07</v>
       </c>
-      <c r="I81" s="23">
+      <c r="I81" s="20">
         <v>1.06</v>
       </c>
-      <c r="J81" s="23">
+      <c r="J81" s="20">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K81" s="23">
+      <c r="K81" s="20">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L81" s="23">
+      <c r="L81" s="20">
         <v>1.55</v>
       </c>
-      <c r="M81" s="23">
+      <c r="M81" s="20">
         <v>1.64</v>
       </c>
-      <c r="N81" s="23">
+      <c r="N81" s="20">
         <v>1.65</v>
       </c>
-      <c r="O81" s="23">
+      <c r="O81" s="20">
         <v>1.73</v>
       </c>
-      <c r="P81" s="23">
+      <c r="P81" s="20">
         <v>1.73</v>
       </c>
-      <c r="Q81" s="23">
+      <c r="Q81" s="20">
         <v>1.31</v>
       </c>
-      <c r="R81" s="23">
+      <c r="R81" s="20">
         <v>1.35</v>
       </c>
-      <c r="S81" s="23">
+      <c r="S81" s="20">
         <v>1.44</v>
       </c>
-      <c r="T81" s="23">
+      <c r="T81" s="20">
         <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
+      <c r="A82" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B82" s="19">
+      <c r="B82" s="16">
         <v>-0.01</v>
       </c>
-      <c r="C82" s="23">
+      <c r="C82" s="20">
         <v>0.01</v>
       </c>
-      <c r="D82" s="23">
+      <c r="D82" s="20">
         <v>0.01</v>
       </c>
-      <c r="E82" s="19">
+      <c r="E82" s="16">
         <v>-0.01</v>
       </c>
-      <c r="F82" s="23">
+      <c r="F82" s="20">
         <v>0.02</v>
       </c>
-      <c r="G82" s="23">
+      <c r="G82" s="20">
         <v>0.04</v>
       </c>
-      <c r="H82" s="23">
+      <c r="H82" s="20">
         <v>0.04</v>
       </c>
-      <c r="I82" s="23">
+      <c r="I82" s="20">
         <v>0.03</v>
       </c>
-      <c r="J82" s="23">
+      <c r="J82" s="20">
         <v>0.05</v>
       </c>
-      <c r="K82" s="23">
+      <c r="K82" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L82" s="23">
+      <c r="L82" s="20">
         <v>0.25</v>
       </c>
-      <c r="M82" s="23">
+      <c r="M82" s="20">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N82" s="23">
+      <c r="N82" s="20">
         <v>0.3</v>
       </c>
-      <c r="O82" s="23">
+      <c r="O82" s="20">
         <v>0.33</v>
       </c>
-      <c r="P82" s="23">
+      <c r="P82" s="20">
         <v>0.35</v>
       </c>
-      <c r="Q82" s="23">
+      <c r="Q82" s="20">
         <v>0.18</v>
       </c>
-      <c r="R82" s="23">
+      <c r="R82" s="20">
         <v>0.2</v>
       </c>
-      <c r="S82" s="23">
+      <c r="S82" s="20">
         <v>0.24</v>
       </c>
-      <c r="T82" s="23">
+      <c r="T82" s="20">
         <v>0.11</v>
       </c>
     </row>
     <row r="83" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="14"/>
-      <c r="O83" s="14"/>
-      <c r="P83" s="14"/>
-      <c r="Q83" s="14"/>
-      <c r="R83" s="14"/>
-      <c r="S83" s="14"/>
-      <c r="T83" s="14"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+      <c r="N83" s="11"/>
+      <c r="O83" s="11"/>
+      <c r="P83" s="11"/>
+      <c r="Q83" s="11"/>
+      <c r="R83" s="11"/>
+      <c r="S83" s="11"/>
+      <c r="T83" s="11"/>
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B84" s="20">
         <v>8.76</v>
       </c>
-      <c r="C84" s="23">
+      <c r="C84" s="20">
         <v>9.94</v>
       </c>
-      <c r="D84" s="23">
+      <c r="D84" s="20">
         <v>6.24</v>
       </c>
-      <c r="E84" s="23">
+      <c r="E84" s="20">
         <v>9.6199999999999992</v>
       </c>
-      <c r="F84" s="23">
+      <c r="F84" s="20">
         <v>9.98</v>
       </c>
-      <c r="G84" s="23">
+      <c r="G84" s="20">
         <v>9.49</v>
       </c>
-      <c r="H84" s="23">
+      <c r="H84" s="20">
         <v>6.22</v>
       </c>
-      <c r="I84" s="23">
+      <c r="I84" s="20">
         <v>10.88</v>
       </c>
-      <c r="J84" s="23">
+      <c r="J84" s="20">
         <v>10.69</v>
       </c>
-      <c r="K84" s="23">
+      <c r="K84" s="20">
         <v>10.33</v>
       </c>
-      <c r="L84" s="23">
+      <c r="L84" s="20">
         <v>6.48</v>
       </c>
-      <c r="M84" s="23">
+      <c r="M84" s="20">
         <v>12.49</v>
       </c>
-      <c r="N84" s="23">
+      <c r="N84" s="20">
         <v>10.93</v>
       </c>
-      <c r="O84" s="23">
+      <c r="O84" s="20">
         <v>10.01</v>
       </c>
-      <c r="P84" s="23">
+      <c r="P84" s="20">
         <v>6.92</v>
       </c>
-      <c r="Q84" s="23">
+      <c r="Q84" s="20">
         <v>10.19</v>
       </c>
-      <c r="R84" s="23">
+      <c r="R84" s="20">
         <v>7.18</v>
       </c>
-      <c r="S84" s="16"/>
-      <c r="T84" s="16"/>
+      <c r="S84" s="13"/>
+      <c r="T84" s="13"/>
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B85" s="20">
         <v>41.77</v>
       </c>
-      <c r="C85" s="23">
+      <c r="C85" s="20">
         <v>36.83</v>
       </c>
-      <c r="D85" s="23">
+      <c r="D85" s="20">
         <v>58.68</v>
       </c>
-      <c r="E85" s="23">
+      <c r="E85" s="20">
         <v>38.03</v>
       </c>
-      <c r="F85" s="23">
+      <c r="F85" s="20">
         <v>36.68</v>
       </c>
-      <c r="G85" s="23">
+      <c r="G85" s="20">
         <v>38.58</v>
       </c>
-      <c r="H85" s="23">
+      <c r="H85" s="20">
         <v>58.82</v>
       </c>
-      <c r="I85" s="23">
+      <c r="I85" s="20">
         <v>33.630000000000003</v>
       </c>
-      <c r="J85" s="23">
+      <c r="J85" s="20">
         <v>34.24</v>
       </c>
-      <c r="K85" s="23">
+      <c r="K85" s="20">
         <v>35.43</v>
       </c>
-      <c r="L85" s="23">
+      <c r="L85" s="20">
         <v>56.48</v>
       </c>
-      <c r="M85" s="23">
+      <c r="M85" s="20">
         <v>29.3</v>
       </c>
-      <c r="N85" s="23">
+      <c r="N85" s="20">
         <v>33.49</v>
       </c>
-      <c r="O85" s="23">
+      <c r="O85" s="20">
         <v>36.57</v>
       </c>
-      <c r="P85" s="23">
+      <c r="P85" s="20">
         <v>52.86</v>
       </c>
-      <c r="Q85" s="23">
+      <c r="Q85" s="20">
         <v>35.92</v>
       </c>
-      <c r="R85" s="23">
+      <c r="R85" s="20">
         <v>50.95</v>
       </c>
-      <c r="S85" s="16"/>
-      <c r="T85" s="16"/>
+      <c r="S85" s="13"/>
+      <c r="T85" s="13"/>
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B86" s="20">
         <v>17.57</v>
       </c>
-      <c r="C86" s="23">
+      <c r="C86" s="20">
         <v>16.670000000000002</v>
       </c>
-      <c r="D86" s="23">
+      <c r="D86" s="20">
         <v>15.56</v>
       </c>
-      <c r="E86" s="23">
+      <c r="E86" s="20">
         <v>11.64</v>
       </c>
-      <c r="F86" s="23">
+      <c r="F86" s="20">
         <v>12.76</v>
       </c>
-      <c r="G86" s="23">
+      <c r="G86" s="20">
         <v>7.99</v>
       </c>
-      <c r="H86" s="23">
+      <c r="H86" s="20">
         <v>9.89</v>
       </c>
-      <c r="I86" s="23">
+      <c r="I86" s="20">
         <v>9.4</v>
       </c>
-      <c r="J86" s="23">
+      <c r="J86" s="20">
         <v>7.75</v>
       </c>
-      <c r="K86" s="23">
+      <c r="K86" s="20">
         <v>6.46</v>
       </c>
-      <c r="L86" s="23">
+      <c r="L86" s="20">
         <v>8.08</v>
       </c>
-      <c r="M86" s="23">
+      <c r="M86" s="20">
         <v>16.93</v>
       </c>
-      <c r="N86" s="23">
+      <c r="N86" s="20">
         <v>12.66</v>
       </c>
-      <c r="O86" s="23">
+      <c r="O86" s="20">
         <v>17.09</v>
       </c>
-      <c r="P86" s="23">
+      <c r="P86" s="20">
         <v>13.01</v>
       </c>
-      <c r="Q86" s="23">
+      <c r="Q86" s="20">
         <v>22.18</v>
       </c>
-      <c r="R86" s="23">
+      <c r="R86" s="20">
         <v>38.200000000000003</v>
       </c>
-      <c r="S86" s="16"/>
-      <c r="T86" s="16"/>
+      <c r="S86" s="13"/>
+      <c r="T86" s="13"/>
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B87" s="20">
         <v>20.83</v>
       </c>
-      <c r="C87" s="23">
+      <c r="C87" s="20">
         <v>21.96</v>
       </c>
-      <c r="D87" s="23">
+      <c r="D87" s="20">
         <v>23.52</v>
       </c>
-      <c r="E87" s="23">
+      <c r="E87" s="20">
         <v>31.46</v>
       </c>
-      <c r="F87" s="23">
+      <c r="F87" s="20">
         <v>28.68</v>
       </c>
-      <c r="G87" s="23">
+      <c r="G87" s="20">
         <v>45.83</v>
       </c>
-      <c r="H87" s="23">
+      <c r="H87" s="20">
         <v>37.01</v>
       </c>
-      <c r="I87" s="23">
+      <c r="I87" s="20">
         <v>38.93</v>
       </c>
-      <c r="J87" s="23">
+      <c r="J87" s="20">
         <v>47.21</v>
       </c>
-      <c r="K87" s="23">
+      <c r="K87" s="20">
         <v>56.65</v>
       </c>
-      <c r="L87" s="23">
+      <c r="L87" s="20">
         <v>45.3</v>
       </c>
-      <c r="M87" s="23">
+      <c r="M87" s="20">
         <v>21.62</v>
       </c>
-      <c r="N87" s="23">
+      <c r="N87" s="20">
         <v>28.92</v>
       </c>
-      <c r="O87" s="23">
+      <c r="O87" s="20">
         <v>21.42</v>
       </c>
-      <c r="P87" s="23">
+      <c r="P87" s="20">
         <v>28.14</v>
       </c>
-      <c r="Q87" s="23">
+      <c r="Q87" s="20">
         <v>16.5</v>
       </c>
-      <c r="R87" s="23">
+      <c r="R87" s="20">
         <v>9.58</v>
       </c>
-      <c r="S87" s="16"/>
-      <c r="T87" s="16"/>
+      <c r="S87" s="13"/>
+      <c r="T87" s="13"/>
     </row>
     <row r="88" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B88" s="20">
         <v>20.94</v>
       </c>
-      <c r="C88" s="23">
+      <c r="C88" s="20">
         <v>14.88</v>
       </c>
-      <c r="D88" s="23">
+      <c r="D88" s="20">
         <v>35.159999999999997</v>
       </c>
-      <c r="E88" s="23">
+      <c r="E88" s="20">
         <v>6.57</v>
       </c>
-      <c r="F88" s="23">
+      <c r="F88" s="20">
         <v>8</v>
       </c>
-      <c r="G88" s="19">
+      <c r="G88" s="16">
         <v>-7.25</v>
       </c>
-      <c r="H88" s="23">
+      <c r="H88" s="20">
         <v>21.82</v>
       </c>
-      <c r="I88" s="19">
+      <c r="I88" s="16">
         <v>-5.3</v>
       </c>
-      <c r="J88" s="19">
+      <c r="J88" s="16">
         <v>-12.97</v>
       </c>
-      <c r="K88" s="19">
+      <c r="K88" s="16">
         <v>-21.22</v>
       </c>
-      <c r="L88" s="23">
+      <c r="L88" s="20">
         <v>11.17</v>
       </c>
-      <c r="M88" s="23">
+      <c r="M88" s="20">
         <v>7.68</v>
       </c>
-      <c r="N88" s="23">
+      <c r="N88" s="20">
         <v>4.57</v>
       </c>
-      <c r="O88" s="23">
+      <c r="O88" s="20">
         <v>15.15</v>
       </c>
-      <c r="P88" s="23">
+      <c r="P88" s="20">
         <v>24.72</v>
       </c>
-      <c r="Q88" s="23">
+      <c r="Q88" s="20">
         <v>19.420000000000002</v>
       </c>
-      <c r="R88" s="23">
+      <c r="R88" s="20">
         <v>41.37</v>
       </c>
-      <c r="S88" s="16"/>
-      <c r="T88" s="16"/>
+      <c r="S88" s="13"/>
+      <c r="T88" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="T12"/>
-    <mergeCell ref="T13"/>
-    <mergeCell ref="T14"/>
-    <mergeCell ref="T15"/>
-    <mergeCell ref="R12"/>
-    <mergeCell ref="R13"/>
-    <mergeCell ref="R14"/>
-    <mergeCell ref="R15"/>
-    <mergeCell ref="S12"/>
-    <mergeCell ref="S13"/>
-    <mergeCell ref="S14"/>
-    <mergeCell ref="S15"/>
-    <mergeCell ref="P12"/>
-    <mergeCell ref="P13"/>
-    <mergeCell ref="P14"/>
-    <mergeCell ref="P15"/>
-    <mergeCell ref="Q12"/>
-    <mergeCell ref="Q13"/>
-    <mergeCell ref="Q14"/>
-    <mergeCell ref="Q15"/>
-    <mergeCell ref="N12"/>
-    <mergeCell ref="N13"/>
-    <mergeCell ref="N14"/>
-    <mergeCell ref="N15"/>
-    <mergeCell ref="O12"/>
-    <mergeCell ref="O13"/>
-    <mergeCell ref="O14"/>
-    <mergeCell ref="O15"/>
-    <mergeCell ref="L12"/>
-    <mergeCell ref="L13"/>
-    <mergeCell ref="L14"/>
-    <mergeCell ref="L15"/>
-    <mergeCell ref="M12"/>
-    <mergeCell ref="M13"/>
-    <mergeCell ref="M14"/>
-    <mergeCell ref="M15"/>
-    <mergeCell ref="J14"/>
-    <mergeCell ref="J15"/>
-    <mergeCell ref="K12"/>
-    <mergeCell ref="K13"/>
-    <mergeCell ref="K14"/>
-    <mergeCell ref="K15"/>
-    <mergeCell ref="H15"/>
-    <mergeCell ref="I12"/>
-    <mergeCell ref="I13"/>
-    <mergeCell ref="I14"/>
-    <mergeCell ref="I15"/>
-    <mergeCell ref="F15"/>
-    <mergeCell ref="G12"/>
-    <mergeCell ref="G13"/>
-    <mergeCell ref="G14"/>
-    <mergeCell ref="G15"/>
-    <mergeCell ref="D15"/>
-    <mergeCell ref="E12"/>
-    <mergeCell ref="E13"/>
-    <mergeCell ref="E14"/>
-    <mergeCell ref="E15"/>
-    <mergeCell ref="B15"/>
-    <mergeCell ref="C12"/>
-    <mergeCell ref="C13"/>
-    <mergeCell ref="C14"/>
-    <mergeCell ref="C15"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="L11:O11"/>
     <mergeCell ref="P11:S11"/>
     <mergeCell ref="T11"/>
     <mergeCell ref="B12"/>
@@ -5128,11 +5071,68 @@
     <mergeCell ref="H14"/>
     <mergeCell ref="J12"/>
     <mergeCell ref="J13"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="C12"/>
+    <mergeCell ref="C13"/>
+    <mergeCell ref="C14"/>
+    <mergeCell ref="C15"/>
+    <mergeCell ref="D15"/>
+    <mergeCell ref="E12"/>
+    <mergeCell ref="E13"/>
+    <mergeCell ref="E14"/>
+    <mergeCell ref="E15"/>
+    <mergeCell ref="F15"/>
+    <mergeCell ref="G12"/>
+    <mergeCell ref="G13"/>
+    <mergeCell ref="G14"/>
+    <mergeCell ref="G15"/>
+    <mergeCell ref="H15"/>
+    <mergeCell ref="I12"/>
+    <mergeCell ref="I13"/>
+    <mergeCell ref="I14"/>
+    <mergeCell ref="I15"/>
+    <mergeCell ref="J14"/>
+    <mergeCell ref="J15"/>
+    <mergeCell ref="K12"/>
+    <mergeCell ref="K13"/>
+    <mergeCell ref="K14"/>
+    <mergeCell ref="K15"/>
+    <mergeCell ref="L12"/>
+    <mergeCell ref="L13"/>
+    <mergeCell ref="L14"/>
+    <mergeCell ref="L15"/>
+    <mergeCell ref="M12"/>
+    <mergeCell ref="M13"/>
+    <mergeCell ref="M14"/>
+    <mergeCell ref="M15"/>
+    <mergeCell ref="N12"/>
+    <mergeCell ref="N13"/>
+    <mergeCell ref="N14"/>
+    <mergeCell ref="N15"/>
+    <mergeCell ref="O12"/>
+    <mergeCell ref="O13"/>
+    <mergeCell ref="O14"/>
+    <mergeCell ref="O15"/>
+    <mergeCell ref="P12"/>
+    <mergeCell ref="P13"/>
+    <mergeCell ref="P14"/>
+    <mergeCell ref="P15"/>
+    <mergeCell ref="Q12"/>
+    <mergeCell ref="Q13"/>
+    <mergeCell ref="Q14"/>
+    <mergeCell ref="Q15"/>
+    <mergeCell ref="T12"/>
+    <mergeCell ref="T13"/>
+    <mergeCell ref="T14"/>
+    <mergeCell ref="T15"/>
+    <mergeCell ref="R12"/>
+    <mergeCell ref="R13"/>
+    <mergeCell ref="R14"/>
+    <mergeCell ref="R15"/>
+    <mergeCell ref="S12"/>
+    <mergeCell ref="S13"/>
+    <mergeCell ref="S14"/>
+    <mergeCell ref="S15"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.75"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
